--- a/submission/knowledge/A04-武汉美食顾问/武汉美食顾问QA导入表.xlsx
+++ b/submission/knowledge/A04-武汉美食顾问/武汉美食顾问QA导入表.xlsx
@@ -877,6 +877,210 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">周黑鸭是老字号吗？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">它是源于武汉的连锁卤味品牌。不要把它说成与老通城同一批中华老字号，除非你核对到商务部名录。预包装相对好带。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸭脖</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能带上高铁吗？</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">预包装看铁路规定和气味限制。不保证。散称渗油更麻烦。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸭脖</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">面窝是什么？</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">油炸米面圆饼，过早配角。不是必须点。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">面窝</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晚上吃什么？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小龙虾、烧烤偏正餐宵夜，不是过早。看店证照。回程问管家。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宵夜</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必点藕汤吗？</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家常正餐常见，不是过早必点。</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">藕汤</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">下雨还去户部巷吗？</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不必。可改商场或机场公示门店。</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨天</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精武和周黑鸭哪个好？</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都是市场品牌，我不排名。选预包装、看日期。</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精武</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉庆街就是户部巷吗？</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。户部巷在武昌，吉庆街在汉口，功能也不同。</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吉庆街</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">芝麻过敏怎么过早？</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明确告诉店员。可改其他面食或豆皮。我不编食谱。</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">忌口</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">热干面一定很辣吗？</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辣椒油常另加，可以要求不放。</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辣椒</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必须点面窝吗？</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。它是油炸配角。</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">配菜</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">来不及出站？</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">站内有证门店即可。以当日营业为准。</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">站内</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>